--- a/ZYQDManager/wwwroot/Templates/遮阳检验报告-电机测试新.xlsx
+++ b/ZYQDManager/wwwroot/Templates/遮阳检验报告-电机测试新.xlsx
@@ -827,7 +827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -973,6 +973,132 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1000,84 +1126,12 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1105,56 +1159,29 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1612,7 +1639,7 @@
       <c r="E15" s="20"/>
       <c r="F15" s="20"/>
       <c r="G15" s="43"/>
-      <c r="H15" s="82"/>
+      <c r="H15" s="90"/>
       <c r="I15" s="21" t="s">
         <v>61</v>
       </c>
@@ -1634,7 +1661,7 @@
       <c r="E16" s="25"/>
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="83"/>
+      <c r="H16" s="91"/>
       <c r="I16" s="26" t="s">
         <v>60</v>
       </c>
@@ -1656,7 +1683,7 @@
       <c r="E17" s="25"/>
       <c r="F17" s="28"/>
       <c r="G17" s="28"/>
-      <c r="H17" s="82"/>
+      <c r="H17" s="90"/>
       <c r="I17" s="21" t="s">
         <v>58</v>
       </c>
@@ -1676,7 +1703,7 @@
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="28"/>
-      <c r="H18" s="83"/>
+      <c r="H18" s="91"/>
       <c r="I18" s="26" t="s">
         <v>57</v>
       </c>
@@ -1698,7 +1725,7 @@
       <c r="E19" s="20"/>
       <c r="F19" s="20"/>
       <c r="G19" s="43"/>
-      <c r="H19" s="82"/>
+      <c r="H19" s="90"/>
       <c r="I19" s="21" t="s">
         <v>55</v>
       </c>
@@ -1715,12 +1742,12 @@
         <v>54</v>
       </c>
       <c r="B20" s="24"/>
-      <c r="C20" s="96"/>
-      <c r="D20" s="96"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
       <c r="E20" s="25"/>
       <c r="F20" s="28"/>
       <c r="G20" s="28"/>
-      <c r="H20" s="83"/>
+      <c r="H20" s="91"/>
       <c r="I20" s="26" t="s">
         <v>53</v>
       </c>
@@ -1742,7 +1769,7 @@
       <c r="E21" s="25"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28"/>
-      <c r="H21" s="82"/>
+      <c r="H21" s="90"/>
       <c r="I21" s="21" t="s">
         <v>51</v>
       </c>
@@ -1764,7 +1791,7 @@
       <c r="E22" s="25"/>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
-      <c r="H22" s="83"/>
+      <c r="H22" s="91"/>
       <c r="I22" s="26" t="s">
         <v>49</v>
       </c>
@@ -1779,7 +1806,7 @@
     <row r="23" spans="1:16" s="2" customFormat="1" ht="12.75" customHeight="1">
       <c r="A23" s="11"/>
       <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
+      <c r="C23" s="28"/>
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
       <c r="F23" s="25"/>
@@ -1795,17 +1822,17 @@
       <c r="P23" s="25"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="27" customHeight="1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="129" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="97"/>
-      <c r="D24" s="31" t="s">
+      <c r="B24" s="130"/>
+      <c r="C24" s="127"/>
+      <c r="D24" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="90"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="92"/>
+      <c r="E24" s="98"/>
+      <c r="F24" s="99"/>
+      <c r="G24" s="100"/>
       <c r="H24" s="31" t="s">
         <v>46</v>
       </c>
@@ -1813,23 +1840,23 @@
       <c r="J24" s="32"/>
       <c r="K24" s="32"/>
       <c r="L24" s="32"/>
-      <c r="M24" s="84"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="86"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="93"/>
+      <c r="O24" s="93"/>
+      <c r="P24" s="94"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="27" customHeight="1">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="33" t="s">
+      <c r="B25" s="132"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="125" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="93"/>
-      <c r="F25" s="94"/>
-      <c r="G25" s="95"/>
+      <c r="E25" s="101"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="103"/>
       <c r="H25" s="33" t="s">
         <v>43</v>
       </c>
@@ -1837,23 +1864,23 @@
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="34"/>
-      <c r="M25" s="87"/>
-      <c r="N25" s="88"/>
-      <c r="O25" s="88"/>
-      <c r="P25" s="89"/>
+      <c r="M25" s="95"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="97"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="27" customHeight="1">
       <c r="A26" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B26" s="21"/>
-      <c r="C26" s="97"/>
+      <c r="C26" s="126"/>
       <c r="D26" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="74"/>
+      <c r="E26" s="83"/>
+      <c r="F26" s="84"/>
+      <c r="G26" s="85"/>
       <c r="H26" s="31" t="s">
         <v>40</v>
       </c>
@@ -1861,23 +1888,23 @@
       <c r="J26" s="32"/>
       <c r="K26" s="32"/>
       <c r="L26" s="32"/>
-      <c r="M26" s="90"/>
-      <c r="N26" s="91"/>
-      <c r="O26" s="91"/>
-      <c r="P26" s="92"/>
+      <c r="M26" s="98"/>
+      <c r="N26" s="99"/>
+      <c r="O26" s="99"/>
+      <c r="P26" s="100"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="27" customHeight="1">
       <c r="A27" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B27" s="26"/>
-      <c r="C27" s="97"/>
+      <c r="C27" s="104"/>
       <c r="D27" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="E27" s="75"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="77"/>
+      <c r="E27" s="86"/>
+      <c r="F27" s="87"/>
+      <c r="G27" s="88"/>
       <c r="H27" s="33" t="s">
         <v>79</v>
       </c>
@@ -1885,23 +1912,23 @@
       <c r="J27" s="34"/>
       <c r="K27" s="34"/>
       <c r="L27" s="34"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="94"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="95"/>
+      <c r="M27" s="101"/>
+      <c r="N27" s="102"/>
+      <c r="O27" s="102"/>
+      <c r="P27" s="103"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="27" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B28" s="21"/>
-      <c r="C28" s="109"/>
+      <c r="C28" s="66"/>
       <c r="D28" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="84"/>
-      <c r="F28" s="85"/>
-      <c r="G28" s="86"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="93"/>
+      <c r="G28" s="94"/>
       <c r="H28" s="31" t="s">
         <v>35</v>
       </c>
@@ -1909,23 +1936,23 @@
       <c r="J28" s="32"/>
       <c r="K28" s="32"/>
       <c r="L28" s="36"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="91"/>
-      <c r="P28" s="92"/>
+      <c r="M28" s="98"/>
+      <c r="N28" s="99"/>
+      <c r="O28" s="99"/>
+      <c r="P28" s="100"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="27" customHeight="1">
       <c r="A29" s="9" t="s">
         <v>77</v>
       </c>
       <c r="B29" s="26"/>
-      <c r="C29" s="109"/>
+      <c r="C29" s="66"/>
       <c r="D29" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="E29" s="87"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="89"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="96"/>
+      <c r="G29" s="97"/>
       <c r="H29" s="33" t="s">
         <v>80</v>
       </c>
@@ -1933,10 +1960,10 @@
       <c r="J29" s="34"/>
       <c r="K29" s="34"/>
       <c r="L29" s="37"/>
-      <c r="M29" s="93"/>
-      <c r="N29" s="94"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="95"/>
+      <c r="M29" s="101"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="103"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1">
       <c r="A30" s="3"/>
@@ -2009,18 +2036,18 @@
       <c r="D33" s="41"/>
       <c r="E33" s="52"/>
       <c r="F33" s="29"/>
-      <c r="G33" s="80" t="s">
+      <c r="G33" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="72"/>
-      <c r="K33" s="73"/>
-      <c r="L33" s="73"/>
-      <c r="M33" s="73"/>
-      <c r="N33" s="73"/>
-      <c r="O33" s="73"/>
-      <c r="P33" s="74"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="115"/>
+      <c r="J33" s="83"/>
+      <c r="K33" s="84"/>
+      <c r="L33" s="84"/>
+      <c r="M33" s="84"/>
+      <c r="N33" s="84"/>
+      <c r="O33" s="84"/>
+      <c r="P33" s="85"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1">
       <c r="A34" s="42"/>
@@ -2031,18 +2058,18 @@
       <c r="D34" s="41"/>
       <c r="E34" s="52"/>
       <c r="F34" s="28"/>
-      <c r="G34" s="78" t="s">
+      <c r="G34" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="H34" s="79"/>
-      <c r="I34" s="79"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="76"/>
-      <c r="L34" s="76"/>
-      <c r="M34" s="76"/>
-      <c r="N34" s="76"/>
-      <c r="O34" s="76"/>
-      <c r="P34" s="77"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="86"/>
+      <c r="K34" s="87"/>
+      <c r="L34" s="87"/>
+      <c r="M34" s="87"/>
+      <c r="N34" s="87"/>
+      <c r="O34" s="87"/>
+      <c r="P34" s="88"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1">
       <c r="A35" s="42"/>
@@ -2053,18 +2080,18 @@
       <c r="D35" s="41"/>
       <c r="E35" s="52"/>
       <c r="F35" s="29"/>
-      <c r="G35" s="80" t="s">
+      <c r="G35" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="H35" s="81"/>
-      <c r="I35" s="81"/>
-      <c r="J35" s="72"/>
-      <c r="K35" s="73"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="73"/>
-      <c r="N35" s="73"/>
-      <c r="O35" s="73"/>
-      <c r="P35" s="74"/>
+      <c r="H35" s="115"/>
+      <c r="I35" s="115"/>
+      <c r="J35" s="83"/>
+      <c r="K35" s="84"/>
+      <c r="L35" s="84"/>
+      <c r="M35" s="84"/>
+      <c r="N35" s="84"/>
+      <c r="O35" s="84"/>
+      <c r="P35" s="85"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1">
       <c r="A36" s="42"/>
@@ -2075,18 +2102,18 @@
       <c r="D36" s="41"/>
       <c r="E36" s="52"/>
       <c r="F36" s="28"/>
-      <c r="G36" s="78" t="s">
+      <c r="G36" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="76"/>
-      <c r="L36" s="76"/>
-      <c r="M36" s="76"/>
-      <c r="N36" s="76"/>
-      <c r="O36" s="76"/>
-      <c r="P36" s="77"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="86"/>
+      <c r="K36" s="87"/>
+      <c r="L36" s="87"/>
+      <c r="M36" s="87"/>
+      <c r="N36" s="87"/>
+      <c r="O36" s="87"/>
+      <c r="P36" s="88"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1">
       <c r="A37" s="42"/>
@@ -2097,18 +2124,18 @@
       <c r="D37" s="41"/>
       <c r="E37" s="52"/>
       <c r="F37" s="29"/>
-      <c r="G37" s="80" t="s">
+      <c r="G37" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="H37" s="81"/>
-      <c r="I37" s="81"/>
-      <c r="J37" s="72"/>
-      <c r="K37" s="73"/>
-      <c r="L37" s="73"/>
-      <c r="M37" s="73"/>
-      <c r="N37" s="73"/>
-      <c r="O37" s="73"/>
-      <c r="P37" s="74"/>
+      <c r="H37" s="115"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="84"/>
+      <c r="L37" s="84"/>
+      <c r="M37" s="84"/>
+      <c r="N37" s="84"/>
+      <c r="O37" s="84"/>
+      <c r="P37" s="85"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1">
       <c r="A38" s="42"/>
@@ -2119,113 +2146,113 @@
       <c r="D38" s="41"/>
       <c r="E38" s="52"/>
       <c r="F38" s="29"/>
-      <c r="G38" s="78" t="s">
+      <c r="G38" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="H38" s="79"/>
-      <c r="I38" s="123"/>
-      <c r="J38" s="75"/>
-      <c r="K38" s="76"/>
-      <c r="L38" s="76"/>
-      <c r="M38" s="76"/>
-      <c r="N38" s="76"/>
-      <c r="O38" s="76"/>
-      <c r="P38" s="77"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="86"/>
+      <c r="K38" s="87"/>
+      <c r="L38" s="87"/>
+      <c r="M38" s="87"/>
+      <c r="N38" s="87"/>
+      <c r="O38" s="87"/>
+      <c r="P38" s="88"/>
     </row>
     <row r="39" spans="1:16" ht="78" customHeight="1">
       <c r="A39" s="60"/>
-      <c r="B39" s="120"/>
-      <c r="C39" s="120"/>
-      <c r="D39" s="120"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="77"/>
+      <c r="D39" s="77"/>
       <c r="E39" s="61"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="120"/>
-      <c r="H39" s="120"/>
-      <c r="I39" s="120"/>
-      <c r="J39" s="120"/>
-      <c r="K39" s="120"/>
-      <c r="L39" s="120"/>
-      <c r="M39" s="120"/>
-      <c r="N39" s="120"/>
-      <c r="O39" s="120"/>
-      <c r="P39" s="120"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
+      <c r="L39" s="77"/>
+      <c r="M39" s="77"/>
+      <c r="N39" s="77"/>
+      <c r="O39" s="77"/>
+      <c r="P39" s="77"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1">
-      <c r="A40" s="63"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
-      <c r="E40" s="65"/>
-      <c r="F40" s="98" t="s">
+      <c r="A40" s="105"/>
+      <c r="B40" s="106"/>
+      <c r="C40" s="106"/>
+      <c r="D40" s="106"/>
+      <c r="E40" s="107"/>
+      <c r="F40" s="116" t="s">
         <v>81</v>
       </c>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="99"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="99"/>
-      <c r="L40" s="99"/>
-      <c r="M40" s="99"/>
-      <c r="N40" s="99"/>
-      <c r="O40" s="99"/>
-      <c r="P40" s="100"/>
+      <c r="G40" s="117"/>
+      <c r="H40" s="117"/>
+      <c r="I40" s="117"/>
+      <c r="J40" s="117"/>
+      <c r="K40" s="117"/>
+      <c r="L40" s="117"/>
+      <c r="M40" s="117"/>
+      <c r="N40" s="117"/>
+      <c r="O40" s="117"/>
+      <c r="P40" s="118"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1">
-      <c r="A41" s="66"/>
-      <c r="B41" s="67"/>
-      <c r="C41" s="67"/>
-      <c r="D41" s="67"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="101"/>
-      <c r="G41" s="102"/>
-      <c r="H41" s="102"/>
-      <c r="I41" s="102"/>
-      <c r="J41" s="102"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="102"/>
-      <c r="M41" s="102"/>
-      <c r="N41" s="102"/>
-      <c r="O41" s="102"/>
-      <c r="P41" s="103"/>
+      <c r="A41" s="108"/>
+      <c r="B41" s="109"/>
+      <c r="C41" s="109"/>
+      <c r="D41" s="109"/>
+      <c r="E41" s="110"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="120"/>
+      <c r="H41" s="120"/>
+      <c r="I41" s="120"/>
+      <c r="J41" s="120"/>
+      <c r="K41" s="120"/>
+      <c r="L41" s="120"/>
+      <c r="M41" s="120"/>
+      <c r="N41" s="120"/>
+      <c r="O41" s="120"/>
+      <c r="P41" s="121"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1">
-      <c r="A42" s="66"/>
-      <c r="B42" s="67"/>
-      <c r="C42" s="67"/>
-      <c r="D42" s="67"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="101"/>
-      <c r="G42" s="102"/>
-      <c r="H42" s="102"/>
-      <c r="I42" s="102"/>
-      <c r="J42" s="102"/>
-      <c r="K42" s="102"/>
-      <c r="L42" s="102"/>
-      <c r="M42" s="102"/>
-      <c r="N42" s="102"/>
-      <c r="O42" s="102"/>
-      <c r="P42" s="103"/>
+      <c r="A42" s="108"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="109"/>
+      <c r="D42" s="109"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="120"/>
+      <c r="H42" s="120"/>
+      <c r="I42" s="120"/>
+      <c r="J42" s="120"/>
+      <c r="K42" s="120"/>
+      <c r="L42" s="120"/>
+      <c r="M42" s="120"/>
+      <c r="N42" s="120"/>
+      <c r="O42" s="120"/>
+      <c r="P42" s="121"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1">
-      <c r="A43" s="69"/>
-      <c r="B43" s="70"/>
-      <c r="C43" s="70"/>
-      <c r="D43" s="70"/>
-      <c r="E43" s="71"/>
-      <c r="F43" s="104"/>
-      <c r="G43" s="105"/>
-      <c r="H43" s="105"/>
-      <c r="I43" s="105"/>
-      <c r="J43" s="105"/>
-      <c r="K43" s="105"/>
-      <c r="L43" s="105"/>
-      <c r="M43" s="105"/>
-      <c r="N43" s="105"/>
-      <c r="O43" s="105"/>
-      <c r="P43" s="106"/>
+      <c r="A43" s="111"/>
+      <c r="B43" s="112"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="112"/>
+      <c r="E43" s="113"/>
+      <c r="F43" s="122"/>
+      <c r="G43" s="123"/>
+      <c r="H43" s="123"/>
+      <c r="I43" s="123"/>
+      <c r="J43" s="123"/>
+      <c r="K43" s="123"/>
+      <c r="L43" s="123"/>
+      <c r="M43" s="123"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="124"/>
     </row>
     <row r="44" spans="1:16" s="3" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A44" s="110" t="s">
+      <c r="A44" s="67" t="s">
         <v>19</v>
       </c>
       <c r="B44" s="5" t="s">
@@ -2236,26 +2263,26 @@
         <v>17</v>
       </c>
       <c r="E44" s="4"/>
-      <c r="F44" s="114" t="s">
+      <c r="F44" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="G44" s="115"/>
-      <c r="H44" s="115"/>
-      <c r="I44" s="115"/>
-      <c r="J44" s="115"/>
-      <c r="K44" s="116"/>
-      <c r="L44" s="114" t="s">
+      <c r="G44" s="72"/>
+      <c r="H44" s="72"/>
+      <c r="I44" s="72"/>
+      <c r="J44" s="72"/>
+      <c r="K44" s="73"/>
+      <c r="L44" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="M44" s="115"/>
-      <c r="N44" s="115"/>
-      <c r="O44" s="116"/>
-      <c r="P44" s="111" t="s">
+      <c r="M44" s="72"/>
+      <c r="N44" s="72"/>
+      <c r="O44" s="73"/>
+      <c r="P44" s="68" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:16" s="3" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A45" s="110"/>
+      <c r="A45" s="67"/>
       <c r="B45" s="55" t="s">
         <v>15</v>
       </c>
@@ -2264,30 +2291,30 @@
         <v>14</v>
       </c>
       <c r="E45" s="56"/>
-      <c r="F45" s="117" t="s">
+      <c r="F45" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="G45" s="118"/>
-      <c r="H45" s="118"/>
-      <c r="I45" s="118"/>
-      <c r="J45" s="118"/>
-      <c r="K45" s="119"/>
-      <c r="L45" s="117" t="s">
+      <c r="G45" s="75"/>
+      <c r="H45" s="75"/>
+      <c r="I45" s="75"/>
+      <c r="J45" s="75"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="M45" s="118"/>
-      <c r="N45" s="118"/>
-      <c r="O45" s="119"/>
-      <c r="P45" s="112"/>
+      <c r="M45" s="75"/>
+      <c r="N45" s="75"/>
+      <c r="O45" s="76"/>
+      <c r="P45" s="69"/>
     </row>
     <row r="46" spans="1:16" ht="13.5" customHeight="1">
-      <c r="A46" s="121" t="s">
+      <c r="A46" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="122"/>
-      <c r="C46" s="122"/>
-      <c r="D46" s="122"/>
-      <c r="E46" s="122"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
       <c r="F46" s="53" t="s">
         <v>1</v>
       </c>
@@ -2318,14 +2345,14 @@
       <c r="O46" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="P46" s="113"/>
+      <c r="P46" s="70"/>
     </row>
     <row r="47" spans="1:16" s="47" customFormat="1" ht="54" customHeight="1">
       <c r="A47" s="45"/>
-      <c r="B47" s="107"/>
-      <c r="C47" s="108"/>
-      <c r="D47" s="107"/>
-      <c r="E47" s="108"/>
+      <c r="B47" s="64"/>
+      <c r="C47" s="65"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="65"/>
       <c r="F47" s="46"/>
       <c r="G47" s="46"/>
       <c r="H47" s="44"/>
@@ -2339,7 +2366,30 @@
       <c r="P47" s="49"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="39">
+    <mergeCell ref="F40:P43"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="J37:P38"/>
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="J35:P36"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="E28:G29"/>
+    <mergeCell ref="M28:P29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="M24:P25"/>
+    <mergeCell ref="M26:P27"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="E24:G25"/>
+    <mergeCell ref="E26:G27"/>
     <mergeCell ref="B47:C47"/>
     <mergeCell ref="D47:E47"/>
     <mergeCell ref="C28:C29"/>
@@ -2355,28 +2405,7 @@
     <mergeCell ref="A46:E46"/>
     <mergeCell ref="G38:I38"/>
     <mergeCell ref="J33:P34"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="M24:P25"/>
-    <mergeCell ref="M26:P27"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="E24:G25"/>
-    <mergeCell ref="E26:G27"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="E28:G29"/>
-    <mergeCell ref="M28:P29"/>
     <mergeCell ref="A40:E43"/>
-    <mergeCell ref="J37:P38"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="J35:P36"/>
-    <mergeCell ref="F40:P43"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
